--- a/docs/samples/search_result_OE-VNL-1001.xlsx
+++ b/docs/samples/search_result_OE-VNL-1001.xlsx
@@ -12,19 +12,21 @@
     <sheet name="归一产品" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="品牌号" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="供应商报价" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="字段来源" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="疑似重复" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="异常清单" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="填写说明" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="库存" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="字段来源" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="疑似重复" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="异常清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="填写说明" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'查询条件'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'归一产品'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'品牌号'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'归一产品'!$A$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'品牌号'!$A$1:$P$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'供应商报价'!$A$1:$M$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'字段来源'!$A$1:$K$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似重复'!$A$1:$S$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'异常清单'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'库存'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'字段来源'!$A$1:$K$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'疑似重复'!$A$1:$S$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'异常清单'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -547,12 +549,71 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-23 19:41</t>
+          <t>2026-09-28 11:40</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>在黄色的 decision / note 列填写后，运行：python manage.py import_review &lt;本文件&gt; --reviewer 姓名</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>疑似重复 decision：merge（确认合并）/ reject（不是同一产品）/ needs_info（待补充资料）；留空表示不处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>“疑似组”相同的行相互关联（同一批相似记录），建议一起对照判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>存在硬冲突的候选若选择 merge，必须在 note 说明理由。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>异常清单 decision：resolve（已解决）/ ignore（忽略）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>任一行填写有误时整份文件不会写入，并逐行提示错误。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -608,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -624,6 +685,8 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -692,6 +755,16 @@
           <t>未处理异常数</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>库存合计</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>图片数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -751,9 +824,13 @@
       <c r="M2" t="n">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M2"/>
+  <autoFilter ref="A1:O2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -764,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -781,6 +858,8 @@
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -854,6 +933,16 @@
           <t>来源定位</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>图片数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -918,6 +1007,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -982,6 +1075,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R2</t>
         </is>
       </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1046,9 +1143,13 @@
           <t>供应商C目录.pdf!p1!t1!r2</t>
         </is>
       </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:P4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1400,6 +1501,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>供应商编号</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>截至日期</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>来源定位</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3239,7 +3407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3615,7 +3783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3745,63 +3913,4 @@
   <autoFilter ref="A1:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>在黄色的 decision / note 列填写后，运行：python manage.py import_review &lt;本文件&gt; --reviewer 姓名</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>疑似重复 decision：merge（确认合并）/ reject（不是同一产品）/ needs_info（待补充资料）；留空表示不处理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>“疑似组”相同的行相互关联（同一批相似记录），建议一起对照判断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>存在硬冲突的候选若选择 merge，必须在 note 说明理由。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>异常清单 decision：resolve（已解决）/ ignore（忽略）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>任一行填写有误时整份文件不会写入，并逐行提示错误。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>